--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488066_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488066_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5725</v>
+        <v>9.175700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6778</v>
+        <v>9.7194</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1053</v>
+        <v>-0.5438</v>
       </c>
       <c r="G2" t="n">
         <v>3.8478</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8112</v>
+        <v>0.792</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3706</v>
+        <v>0.671</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4406</v>
+        <v>0.121</v>
       </c>
       <c r="V2" t="n">
         <v>7.5092</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3983</v>
+        <v>4.0334</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5211</v>
+        <v>3.2966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8772</v>
+        <v>0.7368</v>
       </c>
       <c r="G3" t="n">
         <v>1.1888</v>
@@ -688,13 +688,13 @@
         <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3763</v>
+        <v>0.2588</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1855</v>
+        <v>-0.4101</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8093</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.401</v>
+        <v>1.468</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7265</v>
+        <v>4.3554</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3255</v>
+        <v>-2.8874</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6782</v>
+        <v>0.341</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8263</v>
+        <v>1.6555</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.5045</v>
+        <v>-1.3145</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0295</v>
+        <v>3.4675</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5479</v>
+        <v>2.7845</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5184</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7076</v>
+        <v>-3.1265</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7215</v>
+        <v>-1.129</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9861</v>
+        <v>-1.9975</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1893</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2289</v>
+        <v>0.9287</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6308</v>
+        <v>0.8701</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5981</v>
+        <v>0.0586</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7444</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6302</v>
+        <v>0.9053</v>
       </c>
       <c r="E5" t="n">
-        <v>4.293</v>
+        <v>0.9053</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6628</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.341</v>
+        <v>0.9053</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6555</v>
+        <v>0.3027</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3145</v>
+        <v>0.6027</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4675</v>
+        <v>0.9053</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7845</v>
+        <v>0.3027</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6027</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1265</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.129</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9975</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.091</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8077</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2832</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9053</v>
+        <v>0.8304</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9053</v>
+        <v>0.897</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9053</v>
+        <v>-0.5729</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>-0.1752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>-0.3976</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9053</v>
+        <v>1.0749</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>0.3888</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.6477</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8613</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.7864</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.1524</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.1779</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3303</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519</v>
+        <v>0.2215</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6309</v>
+        <v>-0.3712</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1789</v>
+        <v>0.5927</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5729</v>
+        <v>-1.8073</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1752</v>
+        <v>0.5728</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3976</v>
+        <v>-2.3801</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0749</v>
+        <v>0.3025</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.5001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3888</v>
+        <v>-1.1975</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6477</v>
+        <v>-2.1098</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8613</v>
+        <v>-0.9272</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7864</v>
+        <v>-1.1825</v>
       </c>
       <c r="P7" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R7" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2261</v>
+        <v>1.4252</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.444</v>
+        <v>0.9032</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2179</v>
+        <v>0.522</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5331</v>
+        <v>0.6036</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2827</v>
+        <v>0.1058</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9035</v>
+        <v>0.7121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6208</v>
+        <v>-0.6063</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8073</v>
+        <v>-1.6782</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5728</v>
+        <v>0.8263</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3801</v>
+        <v>-2.5045</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3025</v>
+        <v>1.0295</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5001</v>
+        <v>1.5479</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1975</v>
+        <v>-0.5184</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1098</v>
+        <v>-2.7076</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9272</v>
+        <v>-0.7215</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1825</v>
+        <v>-1.9861</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>0.921</v>
+        <v>1.9336</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3709</v>
+        <v>1.6163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5501</v>
+        <v>0.3173</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6036</v>
+        <v>-0.7444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>-0.7444</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0262</v>
+        <v>-0.6363</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6976</v>
+        <v>1.0032</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7237</v>
+        <v>-1.6395</v>
       </c>
       <c r="G9" t="n">
         <v>1.2318</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8615</v>
+        <v>-0.4717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7488</v>
+        <v>-0.4432</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1128</v>
+        <v>-0.0285</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6036</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4068</v>
+        <v>-2.6715</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3127</v>
+        <v>-2.0364</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9059</v>
+        <v>-0.635</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2358</v>
+        <v>-3.5813</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8888</v>
+        <v>-2.8716</v>
       </c>
       <c r="I10" t="n">
-        <v>1.653</v>
+        <v>-0.7097</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2273</v>
+        <v>-1.9222</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8218</v>
+        <v>-2.0103</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0491</v>
+        <v>0.0881</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4631</v>
+        <v>-1.6591</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.067</v>
+        <v>-0.8613</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3961</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3787</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1372</v>
+        <v>-0.3588</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4244</v>
+        <v>-0.3303</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7128</v>
+        <v>-0.0285</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0704</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1632</v>
+        <v>-2.8539</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4439</v>
+        <v>-3.5352</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7193000000000001</v>
+        <v>0.6813</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5813</v>
+        <v>-1.2358</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8716</v>
+        <v>-2.8888</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7097</v>
+        <v>1.653</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9222</v>
+        <v>0.2273</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.0103</v>
+        <v>-1.8218</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0881</v>
+        <v>2.0491</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6591</v>
+        <v>-1.4631</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8613</v>
+        <v>-1.067</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.3961</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5947</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R11" t="n">
         <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8505</v>
+        <v>0.6902</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7377</v>
+        <v>0.202</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1128</v>
+        <v>0.4881</v>
       </c>
       <c r="V11" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5331</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0616</v>
+        <v>-5.5356</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1085</v>
+        <v>-3.6387</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9531</v>
+        <v>-1.8969</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0813</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2357</v>
+        <v>0.7617</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1176</v>
+        <v>0.5874</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1181</v>
+        <v>0.1743</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.418699999999999</v>
+        <v>5.042800000000004</v>
       </c>
       <c r="E13" t="n">
-        <v>10.68360000000001</v>
+        <v>11.3075</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.2647</v>
+        <v>-6.264699999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-7.4421</v>
@@ -1459,7 +1459,7 @@
         <v>-11.9109</v>
       </c>
       <c r="P13" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.8489</v>
@@ -1468,13 +1468,13 @@
         <v>16.849</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4882</v>
+        <v>6.1121</v>
       </c>
       <c r="T13" t="n">
-        <v>2.864799999999999</v>
+        <v>3.4885</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6233</v>
+        <v>2.6235</v>
       </c>
       <c r="V13" t="n">
         <v>6.3726</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1007</v>
+        <v>4.6381</v>
       </c>
       <c r="E14" t="n">
-        <v>7.414</v>
+        <v>7.9233</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3133</v>
+        <v>-3.2852</v>
       </c>
       <c r="G14" t="n">
         <v>5.8114</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4533</v>
+        <v>-0.9159</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5173</v>
+        <v>-0.4893</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6539</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3367</v>
+        <v>1.7651</v>
       </c>
       <c r="E15" t="n">
-        <v>0.711</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6257</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>2.4387</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5073</v>
+        <v>-0.0789</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2577</v>
+        <v>-0.0331</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PERERIRA</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0548</v>
+        <v>0.4657</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4719</v>
+        <v>0.5187</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5829</v>
+        <v>-0.053</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8312</v>
+        <v>-0.2221</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5832</v>
+        <v>1.033</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.752</v>
+        <v>-1.2551</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2779</v>
+        <v>0.7059</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2377</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0402</v>
+        <v>0.0804</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4467</v>
+        <v>-0.928</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3455</v>
+        <v>0.4075</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7922</v>
+        <v>-1.3355</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964</v>
+        <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>1.294</v>
+        <v>-0.1826</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8591</v>
+        <v>-0.1872</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4349</v>
+        <v>0.0046</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.674</v>
+        <v>-0.1207</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2456</v>
+        <v>0.2317</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5187</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2731</v>
+        <v>-0.4191</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2221</v>
+        <v>2.2039</v>
       </c>
       <c r="H18" t="n">
-        <v>1.033</v>
+        <v>2.5999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2551</v>
+        <v>-0.3961</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7059</v>
+        <v>3.852</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6254999999999999</v>
+        <v>2.5222</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0804</v>
+        <v>1.3298</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.928</v>
+        <v>-1.6481</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4075</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3355</v>
+        <v>-1.7258</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4027</v>
+        <v>-0.5488</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1872</v>
+        <v>-0.545</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2155</v>
+        <v>-0.0038</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1207</v>
+        <v>-1.4234</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1207</v>
+        <v>-0.7494</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>T. PERERIRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0044</v>
+        <v>0.0994</v>
       </c>
       <c r="E19" t="n">
-        <v>0.447</v>
+        <v>-0.343</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4426</v>
+        <v>0.4425</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2039</v>
+        <v>0.8312</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5999</v>
+        <v>1.5832</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3961</v>
+        <v>-0.752</v>
       </c>
       <c r="J19" t="n">
-        <v>3.852</v>
+        <v>1.2779</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5222</v>
+        <v>1.2377</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3298</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6481</v>
+        <v>-0.4467</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.3455</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7258</v>
+        <v>-0.7922</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7761</v>
+        <v>0.3386</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7488</v>
+        <v>0.0441</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0273</v>
+        <v>0.2945</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4234</v>
+        <v>-0.674</v>
       </c>
       <c r="W19" t="n">
         <v>-0.674</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.583</v>
+        <v>-0.0946</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5459</v>
+        <v>0.5689</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1288</v>
+        <v>-0.6635</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1409</v>
+        <v>-0.2003</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2756</v>
+        <v>-0.6078</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8653</v>
+        <v>0.4075</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8392</v>
+        <v>1.8496</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0719</v>
+        <v>-0.6855</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7673</v>
+        <v>2.5351</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6984</v>
+        <v>-2.0499</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7964</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>1.098</v>
+        <v>-2.1276</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1824</v>
+        <v>-0.6185</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4223</v>
+        <v>-0.5056</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2399</v>
+        <v>-0.113</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5098</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7763</v>
+        <v>-0.4828</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7325</v>
+        <v>-0.9728</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2633</v>
+        <v>1.2402</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9959</v>
+        <v>-2.2131</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2003</v>
+        <v>2.1409</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6078</v>
+        <v>0.2756</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4075</v>
+        <v>1.8653</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8496</v>
+        <v>2.8392</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6855</v>
+        <v>2.0719</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5351</v>
+        <v>0.7673</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0499</v>
+        <v>-0.6984</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07770000000000001</v>
+        <v>-1.7964</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1276</v>
+        <v>1.098</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2565</v>
+        <v>-0.2074</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8112</v>
+        <v>0.1167</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4454</v>
+        <v>-0.3241</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7243000000000001</v>
+        <v>-2.5098</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4828</v>
+        <v>-2.7763</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3132</v>
+        <v>-1.7116</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3312</v>
+        <v>-1.702</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6444</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7708</v>
+        <v>-0.8365</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2446</v>
+        <v>0.0723</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5262</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1334</v>
+        <v>-0.409</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3823</v>
+        <v>-0.4168</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2488</v>
+        <v>0.0078</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6374</v>
+        <v>-0.4274</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8623</v>
+        <v>0.4891</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.775</v>
+        <v>-0.9166</v>
       </c>
       <c r="P22" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-3.9645</v>
-      </c>
       <c r="R22" t="n">
-        <v>2.9733</v>
+        <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>1.82</v>
+        <v>-0.1762</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0853</v>
+        <v>-0.3018</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2653</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6287</v>
+        <v>-1.6899</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3438</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7151</v>
+        <v>-1.6899</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3898</v>
+        <v>-2.0946</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1196</v>
+        <v>0.2878</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2701</v>
+        <v>-2.3825</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3191</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4331</v>
+        <v>-1.138</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0608</v>
+        <v>-0.6533</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3724</v>
+        <v>-0.4847</v>
       </c>
       <c r="V23" t="n">
         <v>-0.0252</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.441</v>
+        <v>-3.0208</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2113</v>
+        <v>-2.595</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2297</v>
+        <v>-0.4257</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8365</v>
+        <v>0.062</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0723</v>
+        <v>0.1117</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9088000000000001</v>
+        <v>-0.0498</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.409</v>
+        <v>0.1454</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4168</v>
+        <v>1.2988</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0078</v>
+        <v>-1.1535</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4274</v>
+        <v>-0.0834</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4891</v>
+        <v>-1.1871</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9166</v>
+        <v>1.1037</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9911</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-1.0664</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8112</v>
+        <v>-0.3706</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0945</v>
+        <v>-0.6958</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6899</v>
+        <v>-0.6287</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6899</v>
+        <v>-1.2323</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0042</v>
+        <v>-3.348</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.41</v>
+        <v>-1.5024</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5942</v>
+        <v>-1.8455</v>
       </c>
       <c r="G25" t="n">
-        <v>0.062</v>
+        <v>-2.7708</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1117</v>
+        <v>-2.2446</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0498</v>
+        <v>-0.5262</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1454</v>
+        <v>-0.1334</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2988</v>
+        <v>-0.3823</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1535</v>
+        <v>0.2488</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0834</v>
+        <v>-2.6374</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1871</v>
+        <v>-1.8623</v>
       </c>
       <c r="O25" t="n">
-        <v>1.1037</v>
+        <v>-0.775</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3876</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5858</v>
+        <v>2.9733</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0499</v>
+        <v>-0.2148</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1855</v>
+        <v>0.2517</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8643</v>
+        <v>-0.4664</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6287</v>
+        <v>0.6287</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6036</v>
+        <v>2.3438</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2323</v>
+        <v>-1.7151</v>
       </c>
     </row>
     <row r="26">
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.4188</v>
+        <v>-3.7397</v>
       </c>
       <c r="E26" t="n">
-        <v>6.264800000000001</v>
+        <v>6.264700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.6835</v>
+        <v>-10.0044</v>
       </c>
       <c r="G26" t="n">
-        <v>7.442</v>
+        <v>7.441999999999998</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3582</v>
+        <v>1.358199999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>6.083599999999998</v>
+        <v>6.0836</v>
       </c>
       <c r="J26" t="n">
         <v>20.8536</v>
       </c>
       <c r="K26" t="n">
-        <v>8.942400000000001</v>
+        <v>8.942399999999999</v>
       </c>
       <c r="L26" t="n">
         <v>11.9109</v>
@@ -2470,10 +2470,10 @@
         <v>-7.5844</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.827100000000001</v>
+        <v>-5.8271</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.8488</v>
@@ -2482,16 +2482,16 @@
         <v>16.8489</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.488200000000001</v>
+        <v>-4.8089</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.6236</v>
+        <v>-2.6235</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8647</v>
+        <v>-2.1855</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.3726</v>
+        <v>-6.372599999999999</v>
       </c>
       <c r="W26" t="n">
         <v>4.8838</v>
